--- a/template-import/contoh-template-import.xlsx
+++ b/template-import/contoh-template-import.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO7"/>
+  <dimension ref="A1:BB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -487,19 +487,6 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="18" customWidth="1" min="55" max="55"/>
-    <col width="18" customWidth="1" min="56" max="56"/>
-    <col width="18" customWidth="1" min="57" max="57"/>
-    <col width="18" customWidth="1" min="58" max="58"/>
-    <col width="18" customWidth="1" min="59" max="59"/>
-    <col width="18" customWidth="1" min="60" max="60"/>
-    <col width="18" customWidth="1" min="61" max="61"/>
-    <col width="18" customWidth="1" min="62" max="62"/>
-    <col width="18" customWidth="1" min="63" max="63"/>
-    <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="18" customWidth="1" min="65" max="65"/>
-    <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="18" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,260 +595,195 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Dusun</t>
+          <t>Desa/Kelurahan</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Desa/Kelurahan</t>
+          <t>Kecamatan</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Kecamatan</t>
+          <t>Kode Pos</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Kode Pos</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Jenis Tinggal</t>
+          <t>Jarak Rumah ke Sekolah (KM)</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Alat Transportasi</t>
+          <t>Ayah - Nama</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Telepon</t>
+          <t>Ayah - Tahun Lahir</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Ayah - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>E-Mail</t>
+          <t>Ayah - Pekerjaan</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Lintang</t>
+          <t>Ayah - Penghasilan</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>Bujur</t>
+          <t>Ayah - NIK</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Jarak Rumah ke Sekolah (KM)</t>
+          <t>Ibu - Nama</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Nama</t>
+          <t>Ibu - Tahun Lahir</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Tahun Lahir</t>
+          <t>Ibu - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Jenjang Pendidikan</t>
+          <t>Ibu - Pekerjaan</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Pekerjaan</t>
+          <t>Ibu - Penghasilan</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Penghasilan</t>
+          <t>Ibu - NIK</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - NIK</t>
+          <t>Wali - Nama</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Nama</t>
+          <t>Wali - Tahun Lahir</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Tahun Lahir</t>
+          <t>Wali - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Jenjang Pendidikan</t>
+          <t>Wali - Pekerjaan</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Pekerjaan</t>
+          <t>Wali - Penghasilan</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Penghasilan</t>
+          <t>Wali - NIK</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - NIK</t>
+          <t>Rombel Saat Ini</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Nama</t>
+          <t>Tingkat</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Tahun Lahir</t>
+          <t>No. Seri Ijazah</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Jenjang Pendidikan</t>
+          <t>Penerima KPS</t>
         </is>
       </c>
       <c r="AQ5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Pekerjaan</t>
+          <t>No. KPS</t>
         </is>
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Penghasilan</t>
+          <t>Penerima KIP</t>
         </is>
       </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
-          <t>Wali - NIK</t>
+          <t>Nomor KIP</t>
         </is>
       </c>
       <c r="AT5" s="2" t="inlineStr">
         <is>
-          <t>Rombel Saat Ini</t>
+          <t>Nama di KIP</t>
         </is>
       </c>
       <c r="AU5" s="2" t="inlineStr">
         <is>
-          <t>Tingkat</t>
+          <t>No. Registrasi Akta Lahir</t>
         </is>
       </c>
       <c r="AV5" s="2" t="inlineStr">
         <is>
-          <t>No. Peserta Ujian Nasional</t>
+          <t>Layak PIP (usulan sekolah)</t>
         </is>
       </c>
       <c r="AW5" s="2" t="inlineStr">
         <is>
-          <t>No. Seri Ijazah</t>
+          <t>Alasan Layak PIP</t>
         </is>
       </c>
       <c r="AX5" s="2" t="inlineStr">
         <is>
-          <t>SKHUN</t>
+          <t>Anak ke-berapa</t>
         </is>
       </c>
       <c r="AY5" s="2" t="inlineStr">
         <is>
-          <t>Penerima KPS</t>
+          <t>Jumlah Saudara Kandung</t>
         </is>
       </c>
       <c r="AZ5" s="2" t="inlineStr">
         <is>
-          <t>No. KPS</t>
+          <t>Berat Badan (kg)</t>
         </is>
       </c>
       <c r="BA5" s="2" t="inlineStr">
         <is>
-          <t>Penerima KIP</t>
+          <t>Tinggi Badan (cm)</t>
         </is>
       </c>
       <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>Nomor KIP</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>Nama di KIP</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>Nomor KKS</t>
-        </is>
-      </c>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>No. Registrasi Akta Lahir</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>Nomor Rekening Bank</t>
-        </is>
-      </c>
-      <c r="BH5" s="2" t="inlineStr">
-        <is>
-          <t>Rekening Atas Nama</t>
-        </is>
-      </c>
-      <c r="BI5" s="2" t="inlineStr">
-        <is>
-          <t>Layak PIP (usulan sekolah)</t>
-        </is>
-      </c>
-      <c r="BJ5" s="2" t="inlineStr">
-        <is>
-          <t>Alasan Layak PIP</t>
-        </is>
-      </c>
-      <c r="BK5" s="2" t="inlineStr">
-        <is>
-          <t>Anak ke-berapa</t>
-        </is>
-      </c>
-      <c r="BL5" s="2" t="inlineStr">
-        <is>
-          <t>Jumlah Saudara Kandung</t>
-        </is>
-      </c>
-      <c r="BM5" s="2" t="inlineStr">
-        <is>
-          <t>Berat Badan (kg)</t>
-        </is>
-      </c>
-      <c r="BN5" s="2" t="inlineStr">
-        <is>
-          <t>Tinggi Badan (cm)</t>
-        </is>
-      </c>
-      <c r="BO5" s="2" t="inlineStr">
         <is>
           <t>Lingkar Kepala (cm)</t>
         </is>
@@ -943,157 +865,131 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Contoh</t>
+          <t>Contoh Kelurahan</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Contoh Kelurahan</t>
+          <t>Kec. Contoh</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Kec. Contoh</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15111</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Bersama orang tua</t>
-        </is>
+          <t>081200000001</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Jalan kaki</t>
-        </is>
+          <t>AYAH CONTOH SATU</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1980</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>081200000001</t>
+          <t>SMA / sederajat</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>contoh1@sekolah.sch.id</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>AYAH CONTOH SATU</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>1980</v>
+          <t>Karyawan Swasta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Rp. 1,000,000 - Rp. 1,999,999</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3671010101800001</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>IBU CONTOH SATU</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SMP / sederajat</t>
+        </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>SMA / sederajat</t>
+          <t>Tidak bekerja</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Karyawan Swasta</t>
+          <t>Tidak Berpenghasilan</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Rp. 1,000,000 - Rp. 1,999,999</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3671010101800001</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>IBU CONTOH SATU</t>
-        </is>
-      </c>
-      <c r="AI6" t="n">
-        <v>1982</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>SMP / sederajat</t>
+          <t>3671010101820001</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tidak sekolah</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Tidak bekerja</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Tidak Berpenghasilan</t>
+          <t>&lt; Rp1.000.000</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3671010101820001</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Tidak sekolah</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>&lt; Rp1.000.000</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>7A</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0001/KLU/JP/2013</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0001/KLU/JP/2013</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="BK6" t="n">
+      <c r="AX6" t="n">
         <v>1</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="AY6" t="n">
         <v>2</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="AZ6" t="n">
         <v>40</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BA6" t="n">
         <v>145</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BB6" t="n">
         <v>52</v>
       </c>
     </row>
@@ -1171,147 +1067,122 @@
           <t>4</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Contoh Kelurahan</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Contoh Kelurahan</t>
+          <t>Kec. Contoh</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Kec. Contoh</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>15112</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Bersama orang tua</t>
+          <t>081200000002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Sepeda</t>
-        </is>
+          <t>AYAH CONTOH DUA</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1978</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>081200000002</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>AYAH CONTOH DUA</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>1978</v>
+          <t>SMA / sederajat</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Buruh Harian Lepas</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>&lt; Rp1.000.000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>IBU CONTOH DUA</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>SMA / sederajat</t>
+        </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>SMA / sederajat</t>
+          <t>Ibu Rumah Tangga</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Buruh Harian Lepas</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>&lt; Rp1.000.000</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>IBU CONTOH DUA</t>
-        </is>
-      </c>
-      <c r="AI7" t="n">
-        <v>1981</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>SMA / sederajat</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Ibu Rumah Tangga</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
           <t>Tidak Berpenghasilan</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0001234567890</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>KIP0000000002</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7A</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
+          <t>CONTOH SISWA DUA</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0001234567890</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>KIP0000000002</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>CONTOH SISWA DUA</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>BRI</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>000000000001</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>CONTOH SISWA DUA</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Penerima KIP</t>
         </is>
       </c>
-      <c r="BK7" t="n">
+      <c r="AX7" t="n">
         <v>2</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="AY7" t="n">
         <v>1</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="AZ7" t="n">
         <v>38</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BA7" t="n">
         <v>142</v>
       </c>
     </row>

--- a/template-import/contoh-template-import.xlsx
+++ b/template-import/contoh-template-import.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB7"/>
+  <dimension ref="A1:BA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,6 @@
     <col width="18" customWidth="1" min="51" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,220 +569,215 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Kebutuhan Khusus</t>
+          <t>Sekolah Asal</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Sekolah Asal</t>
+          <t>Alamat (Jalan)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Alamat (Jalan)</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>Desa/Kelurahan</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Desa/Kelurahan</t>
+          <t>Kecamatan</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Kecamatan</t>
+          <t>Kode Pos</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Kode Pos</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jarak Rumah ke Sekolah (KM)</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Jarak Rumah ke Sekolah (KM)</t>
+          <t>Ayah - Nama</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Nama</t>
+          <t>Ayah - Tahun Lahir</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Tahun Lahir</t>
+          <t>Ayah - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Jenjang Pendidikan</t>
+          <t>Ayah - Pekerjaan</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Pekerjaan</t>
+          <t>Ayah - Penghasilan</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - Penghasilan</t>
+          <t>Ayah - NIK</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>Ayah - NIK</t>
+          <t>Ibu - Nama</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Nama</t>
+          <t>Ibu - Tahun Lahir</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Tahun Lahir</t>
+          <t>Ibu - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Jenjang Pendidikan</t>
+          <t>Ibu - Pekerjaan</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Pekerjaan</t>
+          <t>Ibu - Penghasilan</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - Penghasilan</t>
+          <t>Ibu - NIK</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>Ibu - NIK</t>
+          <t>Wali - Nama</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Nama</t>
+          <t>Wali - Tahun Lahir</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Tahun Lahir</t>
+          <t>Wali - Jenjang Pendidikan</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Jenjang Pendidikan</t>
+          <t>Wali - Pekerjaan</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Pekerjaan</t>
+          <t>Wali - Penghasilan</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>Wali - Penghasilan</t>
+          <t>Wali - NIK</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>Wali - NIK</t>
+          <t>Rombel Saat Ini</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>Rombel Saat Ini</t>
+          <t>Tingkat</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>Tingkat</t>
+          <t>No. Seri Ijazah</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>No. Seri Ijazah</t>
+          <t>Penerima KPS</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>Penerima KPS</t>
+          <t>No. KPS</t>
         </is>
       </c>
       <c r="AQ5" s="2" t="inlineStr">
         <is>
-          <t>No. KPS</t>
+          <t>Penerima KIP</t>
         </is>
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>Penerima KIP</t>
+          <t>Nomor KIP</t>
         </is>
       </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
-          <t>Nomor KIP</t>
+          <t>Nama di KIP</t>
         </is>
       </c>
       <c r="AT5" s="2" t="inlineStr">
         <is>
-          <t>Nama di KIP</t>
+          <t>No. Registrasi Akta Lahir</t>
         </is>
       </c>
       <c r="AU5" s="2" t="inlineStr">
         <is>
-          <t>No. Registrasi Akta Lahir</t>
+          <t>Layak PIP (usulan sekolah)</t>
         </is>
       </c>
       <c r="AV5" s="2" t="inlineStr">
         <is>
-          <t>Layak PIP (usulan sekolah)</t>
+          <t>Alasan Layak PIP</t>
         </is>
       </c>
       <c r="AW5" s="2" t="inlineStr">
         <is>
-          <t>Alasan Layak PIP</t>
+          <t>Anak ke-berapa</t>
         </is>
       </c>
       <c r="AX5" s="2" t="inlineStr">
         <is>
-          <t>Anak ke-berapa</t>
+          <t>Jumlah Saudara Kandung</t>
         </is>
       </c>
       <c r="AY5" s="2" t="inlineStr">
         <is>
-          <t>Jumlah Saudara Kandung</t>
+          <t>Berat Badan (kg)</t>
         </is>
       </c>
       <c r="AZ5" s="2" t="inlineStr">
         <is>
-          <t>Berat Badan (kg)</t>
+          <t>Tinggi Badan (cm)</t>
         </is>
       </c>
       <c r="BA5" s="2" t="inlineStr">
-        <is>
-          <t>Tinggi Badan (cm)</t>
-        </is>
-      </c>
-      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>Lingkar Kepala (cm)</t>
         </is>
@@ -840,156 +834,151 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tidak ada</t>
+          <t>SD NEGERI CONTOH 1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SD NEGERI CONTOH 1</t>
+          <t>Jl. Contoh No. 1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Jl. Contoh No. 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Contoh Kelurahan</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Contoh Kelurahan</t>
+          <t>Kec. Contoh</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Kec. Contoh</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>15111</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>081200000001</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="S6" t="n">
         <v>1.5</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>AYAH CONTOH SATU</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="U6" t="n">
         <v>1980</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SMA / sederajat</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SMA / sederajat</t>
+          <t>Karyawan Swasta</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Karyawan Swasta</t>
+          <t>Rp. 1,000,000 - Rp. 1,999,999</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Rp. 1,000,000 - Rp. 1,999,999</t>
+          <t>3671010101800001</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3671010101800001</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
           <t>IBU CONTOH SATU</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AA6" t="n">
         <v>1982</v>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SMP / sederajat</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>SMP / sederajat</t>
+          <t>Tidak bekerja</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Tidak bekerja</t>
+          <t>Tidak Berpenghasilan</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Tidak Berpenghasilan</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
           <t>3671010101820001</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Tidak sekolah</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>&lt; Rp1.000.000</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>7A</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0001/KLU/JP/2013</t>
+        </is>
+      </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0001/KLU/JP/2013</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
           <t>Tidak</t>
         </is>
       </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AZ6" t="n">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="BA6" t="n">
-        <v>145</v>
-      </c>
-      <c r="BB6" t="n">
         <v>52</v>
       </c>
     </row>
@@ -1044,145 +1033,140 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tidak ada</t>
+          <t>SD NEGERI CONTOH 2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SD NEGERI CONTOH 2</t>
+          <t>Jl. Contoh No. 2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Jl. Contoh No. 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Contoh Kelurahan</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Contoh Kelurahan</t>
+          <t>Kec. Contoh</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Kec. Contoh</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>15112</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
           <t>081200000002</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>AYAH CONTOH DUA</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="U7" t="n">
         <v>1978</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SMA / sederajat</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Buruh Harian Lepas</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>&lt; Rp1.000.000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>IBU CONTOH DUA</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>SMA / sederajat</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Buruh Harian Lepas</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>&lt; Rp1.000.000</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>IBU CONTOH DUA</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>1981</v>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>SMA / sederajat</t>
+          <t>Ibu Rumah Tangga</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Ibu Rumah Tangga</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
           <t>Tidak Berpenghasilan</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>7A</t>
         </is>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
       <c r="AP7" t="inlineStr">
         <is>
+          <t>0001234567890</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0001234567890</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>KIP0000000002</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>CONTOH SISWA DUA</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>KIP0000000002</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>CONTOH SISWA DUA</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
           <t>Penerima KIP</t>
         </is>
       </c>
+      <c r="AW7" t="n">
+        <v>2</v>
+      </c>
       <c r="AX7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BA7" t="n">
         <v>142</v>
       </c>
     </row>
